--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>28/07 19:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>19/07 18:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>4.85</t>
-        </is>
+      <c r="F4" t="n">
+        <v>4.85</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>19/07 19:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>19/07 18:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>27/07 17:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>19/07 21:45</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>20/07 00:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>27/07 17:15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>45</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>25/07 16:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>22/07 18:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>19/07 18:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>20/07 09:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>55</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>19/07 13:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>21/07 00:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>19/07 16:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>40</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>55</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>50</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>40</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>19/07 13:10</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F24" t="n">
+        <v>1.55</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>19/07 02:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>8</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>21/07 18:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,97 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45857.078353889</v>
+        <v>45857.07835388889</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Javor IvanjicaSuperLiga (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19/07 18:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+12,9%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45857.14214278643</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Instituto </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Instituto AC Cordoba – River PlateLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20/07 00:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+9,25%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45857.14214278643</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>19/07 18:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>45</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45857.14214278643</v>
+        <v>45857.14214278935</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>20/07 00:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>45</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,97 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45857.14214278643</v>
+        <v>45857.14214278935</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Atletico L</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Atletico Lanus – Rosario CentralLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19/07 19:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+5,93%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45857.1901764022</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 8.5 - tir cadré | FC Dallas </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FC Dallas – St. Louis City SCÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20/07 00:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>41,5%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+5,77%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45857.1901764022</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -1666,10 +1666,8 @@
           <t>19/07 19:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>60</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45857.1901764022</v>
+        <v>45857.19017640047</v>
       </c>
     </row>
     <row r="30">
@@ -1711,10 +1709,8 @@
           <t>20/07 00:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F30" t="n">
+        <v>2.55</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1727,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45857.1901764022</v>
+        <v>45857.19017640047</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,186 @@
         <v>45857.19017640047</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Vitoria BA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Vitoria BA – BragantinoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>20/07 19:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>44,9%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+34,5%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45857.27282052799</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cruzeiro – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20/07 19:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+18,2%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45857.27282052799</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | FC Copenha</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FC Copenhague – KF DritaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+15,3%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45857.27282052799</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Basketball | Moins que 15.51re période2e équipe | Chine (F) </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chine (F) – Japon (F)International - Cpe d'Asie (F)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 15.51re période2e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>19/07 11:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45857.27282052799</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>20/07 19:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45857.27282052799</v>
+        <v>45857.27282053241</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>20/07 19:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F32" t="n">
+        <v>3.1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45857.27282052799</v>
+        <v>45857.27282053241</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>50</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45857.27282052799</v>
+        <v>45857.27282053241</v>
       </c>
     </row>
     <row r="34">
@@ -1887,10 +1881,8 @@
           <t>19/07 11:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.3</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1903,7 +1895,142 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45857.27282052799</v>
+        <v>45857.27282053241</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré1re équipe | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cruzeiro – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20/07 19:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+13,3%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45857.3062348552</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Basketball | H 1 (−23.5)P | Chine (F) </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chine (F) – Japon (F)International - Coupe d'Asie (F)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>H 1 (−23.5)P</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19/07 11:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+12,3%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45857.3062348552</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Palmeiras </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Palmeiras – Atletico MineiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>20/07 20:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>26,2%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45857.3062348552</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>20/07 19:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>4</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45857.3062348552</v>
+        <v>45857.30623484954</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>19/07 11:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
+      <c r="F36" t="n">
+        <v>3.45</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45857.3062348552</v>
+        <v>45857.30623484954</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>20/07 20:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="F37" t="n">
+        <v>4.25</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,187 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45857.3062348552</v>
+        <v>45857.30623484954</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Libertad A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Libertad Asuncion – Nacional AsuncionPrimera Division</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19/07 19:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+67,5%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45857.35342949264</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | Plus que 3.5 - aces2e participant | Francisco </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo – Luciano DarderiATP - Bastad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - aces2e participant</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19/07 12:10</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>54,7%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+9,43%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45857.35342949264</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 3.5 - aces1er participant | Juan Manue</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Juan Manuel Cerundolo – Ignacio BuseATP 250 Gstaad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - aces1er participant</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19/07 09:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>55,8%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+8,90%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45857.35342949264</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Columbus C</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Columbus Crew – DC UnitedMLS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/07 23:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+7,80%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45857.35342949264</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -2053,10 +2053,8 @@
           <t>19/07 19:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>60</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45857.35342949264</v>
+        <v>45857.35342949074</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>19/07 12:10</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45857.35342949264</v>
+        <v>45857.35342949074</v>
       </c>
     </row>
     <row r="40">
@@ -2143,10 +2139,8 @@
           <t>19/07 09:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="F40" t="n">
+        <v>1.95</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2159,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45857.35342949264</v>
+        <v>45857.35342949074</v>
       </c>
     </row>
     <row r="41">
@@ -2188,10 +2182,8 @@
           <t>19/07 23:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>50</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2204,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45857.35342949264</v>
+        <v>45857.35342949074</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2199,6 +2199,141 @@
         <v>45857.35342949074</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 11.5 - tirs2e équipe | Widzew Lod</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Widzew Lodz – Zagłębie Lubin385076e7 Pologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19/07 12:45</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>49,7%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+16,9%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45857.43333989348</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Wisla Ploc</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wisla Plock – Korona KielcePologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19/07 15:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>45,1%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+16,4%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45857.43333989348</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 3.5 - tir cadré1re équipe | GKS Katowi</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GKS Katowice – Rakow CzestochowaPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>19/07 18:15</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>57,8%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+15,6%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45857.43333989348</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>19/07 12:45</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.35</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45857.43333989348</v>
+        <v>45857.43333989583</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>19/07 15:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.58</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45857.43333989348</v>
+        <v>45857.43333989583</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>19/07 18:15</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,97 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45857.43333989348</v>
+        <v>45857.43333989583</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Anderlecht</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Anderlecht – BK HackenLigue Europa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>24/07 18:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+25,4%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45857.47143545867</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 13.5 - tirs1re équipe | Wisla Ploc</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Wisla Plock – Korona KielcePologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19/07 15:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+10,7%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45857.47143545867</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>24/07 18:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>45</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45857.47143545867</v>
+        <v>45857.47143546296</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>19/07 15:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,52 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45857.47143545867</v>
+        <v>45857.47143546296</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cruzeiro – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20/07 19:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>50,2%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+10,4%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45857.53029366258</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>20/07 19:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,52 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45857.53029366258</v>
+        <v>45857.53029365741</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Levski Sof</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Levski Sofia – Sporting BragaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>24/07 17:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+19,6%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45857.56413854031</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -2483,10 +2483,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>50</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45857.56413854031</v>
+        <v>45857.56413854167</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2500,6 +2500,51 @@
         <v>45857.56413854167</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | San Lorenz</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>San Lorenzo – Gimnasia La PlataLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>19/07 17:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+8,86%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45857.64068247918</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -2526,10 +2526,8 @@
           <t>19/07 17:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>60</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45857.64068247918</v>
+        <v>45857.64068247685</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2543,6 +2543,51 @@
         <v>45857.64068247685</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Rionegro A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Rionegro Aguilas – Atletico JuniorPrimera A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>19/07 19:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+12,6%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45857.72258296896</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>19/07 19:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>45</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,97 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45857.72258296896</v>
+        <v>45857.72258297454</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tir cadré | Houston Dy</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Houston Dynamo – Philadelphia UnionÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>20/07 00:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+8,80%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45857.77164951366</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Volleyball | Moins que 3.5 | Allemagne </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Allemagne – BrésilLigue des Nations</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Moins que 3.5</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>20/07 05:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+2,70%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45857.77164951366</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>20/07 00:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F51" t="n">
+        <v>3.9</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45857.77164951366</v>
+        <v>45857.77164951389</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>20/07 05:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.7</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,52 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45857.77164951366</v>
+        <v>45857.77164951389</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Universita</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova – FC Universitatea ClujLiga 1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>28/07 18:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+2,22%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45857.80404714181</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>28/07 18:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>35</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,187 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45857.80404714181</v>
+        <v>45857.8040471412</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Volleyball | H 1 (−9.5) | Ukraine – </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ukraine – CanadaLigue des Nations</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>H 1 (−9.5)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>20/07 11:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>50,4%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+17,3%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45857.8504354582</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball | Moins que 3.5 | Etats-Unis</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Etats-Unis – JaponLigue des Nations</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Moins que 3.5</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20/07 10:20</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+3,08%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45857.8504354582</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 25.5 - tirs | New Englan</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>New England Revolution – Orlando City SCÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19/07 23:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>37,3%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+2,45%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45857.8504354582</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Sporting K</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City – New York City FC385076e7 États-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>20/07 00:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+2,07%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45857.8504354582</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>20/07 11:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
+      <c r="F54" t="n">
+        <v>2.33</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45857.8504354582</v>
+        <v>45857.85043546296</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>20/07 10:20</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.9</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45857.8504354582</v>
+        <v>45857.85043546296</v>
       </c>
     </row>
     <row r="56">
@@ -2831,10 +2827,8 @@
           <t>19/07 23:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F56" t="n">
+        <v>2.75</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2847,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45857.8504354582</v>
+        <v>45857.85043546296</v>
       </c>
     </row>
     <row r="57">
@@ -2876,10 +2870,8 @@
           <t>20/07 00:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F57" t="n">
+        <v>2.4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2892,7 +2884,232 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45857.8504354582</v>
+        <v>45857.85043546296</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Portland T</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Portland Timbers – Minnesota UnitedÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>20/07 02:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>43,7%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+26,6%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45857.88957987461</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Sporting K</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City – New York City FCÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>20/07 00:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+23,8%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45857.88957987461</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | CF Montréa</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CF Montréal – Chicago FireÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>19/07 23:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+15,8%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45857.88957987461</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | Plus que 2.5 - break2e participant | JM.Cerundo</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>JM.Cerundolo – A.BublikATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 2.5 - break2e participant</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>20/07 09:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+9,51%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45857.88957987461</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Hamrun Spa</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hamrun Spartans FC – Dynamo KievLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+4,10%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45857.88957987461</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>20/07 02:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F58" t="n">
+        <v>2.9</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45857.88957987461</v>
+        <v>45857.88957987269</v>
       </c>
     </row>
     <row r="59">
@@ -2958,10 +2956,8 @@
           <t>20/07 00:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F59" t="n">
+        <v>2.95</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2974,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45857.88957987461</v>
+        <v>45857.88957987269</v>
       </c>
     </row>
     <row r="60">
@@ -3003,10 +2999,8 @@
           <t>19/07 23:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3.2</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3019,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45857.88957987461</v>
+        <v>45857.88957987269</v>
       </c>
     </row>
     <row r="61">
@@ -3048,10 +3042,8 @@
           <t>20/07 09:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F61" t="n">
+        <v>1.9</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3064,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45857.88957987461</v>
+        <v>45857.88957987269</v>
       </c>
     </row>
     <row r="62">
@@ -3093,10 +3085,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>45</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3109,7 +3099,142 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45857.88957987461</v>
+        <v>45857.88957987269</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs2e équipe | Portland T</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Portland Timbers – Minnesota UnitedÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>20/07 02:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+11,0%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45857.93176223433</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Water-polo | 2 | Afrique du</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Water-polo</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Afrique du Sud – SingapourMonde - Mondial (H)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>20/07 01:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>72,1%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+2,42%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45857.93176223433</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Barracas C</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Barracas Central – Independiente RivadaviaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>20/07 17:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+2,36%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45857.93176223433</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-19.xlsx
+++ b/data/valuebets_database_2025-07-19.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>20/07 02:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F63" t="n">
+        <v>3.2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45857.93176223433</v>
+        <v>45857.9317622338</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>20/07 01:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="F64" t="n">
+        <v>1.42</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45857.93176223433</v>
+        <v>45857.9317622338</v>
       </c>
     </row>
     <row r="65">
@@ -3218,23 +3214,111 @@
           <t>20/07 17:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="n">
+        <v>40</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+2,36%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45857.9317622338</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Pachuca – </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Pachuca – Mazatlan FCLiga MX</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>26/07 23:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>+2,36%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>45857.93176223433</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+4,86%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45857.97529281095</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Volleyball | H 2 (−8.5) | Turquie – </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Turquie – ArgentineLigue des Nations</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>H 2 (−8.5)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>20/07 02:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>45,2%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+4,44%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45857.97529281095</v>
       </c>
     </row>
   </sheetData>
